--- a/IEF_Home/UploadedFiles/D42_04_RM_ReMeasure_electricity_v1.xlsx
+++ b/IEF_Home/UploadedFiles/D42_04_RM_ReMeasure_electricity_v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8057418F-81C5-4D31-A0FD-BF8250A9D63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{602163F7-9D0E-4B9D-899A-DD5BA5AEDB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="187">
   <si>
     <t>Dataset information</t>
   </si>
@@ -377,9 +377,6 @@
   </si>
   <si>
     <t>Vehicle</t>
-  </si>
-  <si>
-    <t>reuse</t>
   </si>
   <si>
     <t>Mass ratio</t>
@@ -481,9 +478,6 @@
     <t>steel</t>
   </si>
   <si>
-    <t>recycling</t>
-  </si>
-  <si>
     <t>GRO2024_recycling</t>
   </si>
   <si>
@@ -587,9 +581,6 @@
     <t>Assumption based on compilation from scientific literature and expert estimates</t>
   </si>
   <si>
-    <t>use phase - infrastructure</t>
-  </si>
-  <si>
     <t>time</t>
   </si>
   <si>
@@ -603,13 +594,25 @@
   </si>
   <si>
     <t>World</t>
+  </si>
+  <si>
+    <t>use phase - electricity infrastructure</t>
+  </si>
+  <si>
+    <t>mass ratio</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>R3b</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -677,6 +680,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1500,7 +1509,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="34"/>
@@ -1540,7 +1549,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="6" t="s">
@@ -1584,7 +1593,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="6" t="s">
@@ -1606,7 +1615,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="11" t="s">
@@ -1634,7 +1643,7 @@
         <v>26</v>
       </c>
       <c r="D11" s="54" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E11" s="54"/>
       <c r="F11" s="15" t="s">
@@ -1660,11 +1669,11 @@
         <v>31</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="37" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G12" s="38">
         <v>1</v>
@@ -1684,17 +1693,17 @@
         <v>33</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="37" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G13" s="38">
         <v>1</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I13" s="40"/>
       <c r="L13" s="1"/>
@@ -1712,13 +1721,13 @@
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="37" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G14" s="38">
         <v>1</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I14" s="40"/>
       <c r="L14" s="1"/>
@@ -1732,7 +1741,7 @@
         <v>35</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="37" t="s">
@@ -1742,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I15" s="40"/>
       <c r="L15" s="1"/>
@@ -1756,11 +1765,11 @@
         <v>37</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="37" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G16" s="41">
         <v>1</v>
@@ -1780,11 +1789,11 @@
         <v>38</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G17" s="41">
         <v>1</v>
@@ -1801,7 +1810,7 @@
         <v>39</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="34"/>
@@ -1817,7 +1826,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="34"/>
@@ -1851,7 +1860,7 @@
         <v>44</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E21" s="57"/>
       <c r="F21" s="42"/>
@@ -1869,7 +1878,7 @@
         <v>45</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E22" s="57"/>
       <c r="L22" s="1"/>
@@ -1883,7 +1892,7 @@
         <v>46</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E23" s="57"/>
       <c r="L23" s="1"/>
@@ -1929,7 +1938,7 @@
         <v>50</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E26" s="9"/>
       <c r="G26" s="2"/>
@@ -1960,7 +1969,7 @@
         <v>52</v>
       </c>
       <c r="D28" s="35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E28" s="9"/>
       <c r="G28" s="2"/>
@@ -1991,7 +2000,7 @@
         <v>54</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E30" s="9"/>
       <c r="G30" s="2"/>
@@ -2049,7 +2058,7 @@
         <v>58</v>
       </c>
       <c r="D34" s="54" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E34" s="35"/>
       <c r="G34" s="2"/>
@@ -2078,7 +2087,7 @@
         <v>60</v>
       </c>
       <c r="D36" s="54" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E36" s="54"/>
       <c r="G36" s="2"/>
@@ -2328,7 +2337,7 @@
         <v>84</v>
       </c>
       <c r="D53" s="57" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E53" s="57"/>
     </row>
@@ -2341,7 +2350,7 @@
         <v>85</v>
       </c>
       <c r="D54" s="57" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E54" s="57"/>
     </row>
@@ -2590,7 +2599,7 @@
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.453125" style="60" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31" style="60" bestFit="1" customWidth="1"/>
     <col min="2" max="8" width="21.54296875" customWidth="1"/>
     <col min="9" max="11" width="21.54296875" style="60" customWidth="1"/>
     <col min="12" max="13" width="21.54296875" customWidth="1"/>
@@ -2599,34 +2608,34 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="24" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D1" s="24" t="s">
         <v>109</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G1" s="24" t="s">
         <v>32</v>
       </c>
       <c r="H1" s="24" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K1" s="24" t="s">
         <v>36</v>
@@ -2640,22 +2649,22 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B2" s="62" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C2">
         <v>2020</v>
       </c>
       <c r="D2" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E2" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E2" s="62" t="s">
-        <v>145</v>
-      </c>
       <c r="F2" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G2" s="59">
         <v>77</v>
@@ -2676,27 +2685,27 @@
         <v>68</v>
       </c>
       <c r="M2" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B3" s="62" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C3" s="60">
         <v>2020</v>
       </c>
       <c r="D3" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E3" s="62" t="s">
-        <v>145</v>
-      </c>
       <c r="F3" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G3" s="59">
         <v>0</v>
@@ -2717,27 +2726,27 @@
         <v>68</v>
       </c>
       <c r="M3" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B4" s="62" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C4" s="60">
         <v>2020</v>
       </c>
       <c r="D4" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E4" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E4" s="62" t="s">
-        <v>145</v>
-      </c>
       <c r="F4" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G4" s="59">
         <v>25</v>
@@ -2758,27 +2767,27 @@
         <v>68</v>
       </c>
       <c r="M4" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B5" s="62" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C5" s="60">
         <v>2020</v>
       </c>
       <c r="D5" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E5" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E5" s="62" t="s">
-        <v>145</v>
-      </c>
       <c r="F5" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G5" s="59">
         <v>74</v>
@@ -2799,27 +2808,27 @@
         <v>68</v>
       </c>
       <c r="M5" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B6" s="62" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C6" s="60">
         <v>2020</v>
       </c>
       <c r="D6" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E6" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E6" s="62" t="s">
-        <v>145</v>
-      </c>
       <c r="F6" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G6" s="59">
         <v>80</v>
@@ -2840,27 +2849,27 @@
         <v>68</v>
       </c>
       <c r="M6" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B7" s="62" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C7" s="60">
         <v>2020</v>
       </c>
       <c r="D7" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E7" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E7" s="62" t="s">
-        <v>145</v>
-      </c>
       <c r="F7" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G7" s="59">
         <v>46</v>
@@ -2881,27 +2890,27 @@
         <v>68</v>
       </c>
       <c r="M7" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B8" s="62" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C8">
         <v>2050</v>
       </c>
       <c r="D8" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E8" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E8" s="62" t="s">
-        <v>145</v>
-      </c>
       <c r="F8" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G8" s="59">
         <v>93</v>
@@ -2922,27 +2931,27 @@
         <v>68</v>
       </c>
       <c r="M8" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B9" s="62" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C9" s="60">
         <v>2050</v>
       </c>
       <c r="D9" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E9" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E9" s="62" t="s">
-        <v>145</v>
-      </c>
       <c r="F9" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G9" s="59">
         <v>37</v>
@@ -2963,27 +2972,27 @@
         <v>68</v>
       </c>
       <c r="M9" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B10" s="62" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C10" s="60">
         <v>2050</v>
       </c>
       <c r="D10" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E10" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E10" s="62" t="s">
-        <v>145</v>
-      </c>
       <c r="F10" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G10" s="59">
         <v>30</v>
@@ -3004,27 +3013,27 @@
         <v>68</v>
       </c>
       <c r="M10" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B11" s="62" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C11" s="60">
         <v>2050</v>
       </c>
       <c r="D11" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E11" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E11" s="62" t="s">
-        <v>145</v>
-      </c>
       <c r="F11" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G11" s="59">
         <v>91</v>
@@ -3045,27 +3054,27 @@
         <v>68</v>
       </c>
       <c r="M11" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B12" s="62" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C12" s="60">
         <v>2050</v>
       </c>
       <c r="D12" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E12" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E12" s="62" t="s">
-        <v>145</v>
-      </c>
       <c r="F12" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G12" s="59">
         <v>95</v>
@@ -3086,27 +3095,27 @@
         <v>68</v>
       </c>
       <c r="M12" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B13" s="62" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C13" s="60">
         <v>2050</v>
       </c>
       <c r="D13" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E13" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E13" s="62" t="s">
-        <v>145</v>
-      </c>
       <c r="F13" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G13" s="59">
         <v>95</v>
@@ -3127,27 +3136,27 @@
         <v>68</v>
       </c>
       <c r="M13" s="62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B14" s="62" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C14">
         <v>2020</v>
       </c>
       <c r="D14" s="62" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E14" s="62" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="F14" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G14" s="59">
         <v>5.3</v>
@@ -3168,27 +3177,27 @@
         <v>68</v>
       </c>
       <c r="M14" s="62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B15" s="62" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C15" s="60">
         <v>2020</v>
       </c>
       <c r="D15" s="62" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E15" s="62" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="F15" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G15" s="59">
         <v>0</v>
@@ -3209,27 +3218,27 @@
         <v>68</v>
       </c>
       <c r="M15" s="62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B16" s="62" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C16" s="60">
         <v>2020</v>
       </c>
       <c r="D16" s="62" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E16" s="62" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="F16" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G16" s="59">
         <v>10</v>
@@ -3250,27 +3259,27 @@
         <v>68</v>
       </c>
       <c r="M16" s="62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B17" s="62" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C17" s="60">
         <v>2020</v>
       </c>
       <c r="D17" s="62" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E17" s="62" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="F17" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G17" s="59">
         <v>11</v>
@@ -3291,27 +3300,27 @@
         <v>68</v>
       </c>
       <c r="M17" s="62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B18" s="62" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C18" s="60">
         <v>2020</v>
       </c>
       <c r="D18" s="62" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E18" s="62" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="F18" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G18" s="59">
         <v>10.8</v>
@@ -3332,27 +3341,27 @@
         <v>68</v>
       </c>
       <c r="M18" s="62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B19" s="62" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C19" s="60">
         <v>2020</v>
       </c>
       <c r="D19" s="62" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E19" s="62" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="F19" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G19" s="59">
         <v>6</v>
@@ -3373,27 +3382,27 @@
         <v>68</v>
       </c>
       <c r="M19" s="62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B20" s="62" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C20">
         <v>2050</v>
       </c>
       <c r="D20" s="62" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E20" s="62" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="F20" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G20" s="59">
         <v>23.8</v>
@@ -3414,27 +3423,27 @@
         <v>68</v>
       </c>
       <c r="M20" s="62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B21" s="62" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C21" s="60">
         <v>2050</v>
       </c>
       <c r="D21" s="62" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E21" s="62" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="F21" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G21" s="59">
         <v>21</v>
@@ -3455,27 +3464,27 @@
         <v>68</v>
       </c>
       <c r="M21" s="62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B22" s="62" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C22" s="60">
         <v>2050</v>
       </c>
       <c r="D22" s="62" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E22" s="62" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="F22" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G22" s="59">
         <v>45.5</v>
@@ -3496,27 +3505,27 @@
         <v>68</v>
       </c>
       <c r="M22" s="62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B23" s="62" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C23" s="60">
         <v>2050</v>
       </c>
       <c r="D23" s="62" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E23" s="62" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="F23" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G23" s="59">
         <v>33</v>
@@ -3537,27 +3546,27 @@
         <v>68</v>
       </c>
       <c r="M23" s="62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B24" s="62" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C24" s="60">
         <v>2050</v>
       </c>
       <c r="D24" s="62" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E24" s="62" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="F24" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G24" s="59">
         <v>34.5</v>
@@ -3578,27 +3587,27 @@
         <v>68</v>
       </c>
       <c r="M24" s="62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="62" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B25" s="62" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C25" s="60">
         <v>2050</v>
       </c>
       <c r="D25" s="62" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E25" s="62" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="F25" s="62" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="G25" s="59">
         <v>68</v>
@@ -3619,10 +3628,11 @@
         <v>68</v>
       </c>
       <c r="M25" s="62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -3644,33 +3654,33 @@
   <sheetData>
     <row r="1" spans="1:8" s="25" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A1" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="C1" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="D1" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="E1" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="F1" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="G1" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="H1" s="28" t="s">
         <v>124</v>
-      </c>
-      <c r="H1" s="28" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>113</v>
@@ -3685,10 +3695,10 @@
         <v>45265</v>
       </c>
       <c r="F2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" t="s">
         <v>126</v>
-      </c>
-      <c r="G2" t="s">
-        <v>127</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -3696,81 +3706,81 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="G3" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E4" s="30">
         <v>45386</v>
       </c>
       <c r="F4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="G5" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="G6" s="58" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="G7" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="G8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E13" s="30">
         <v>45406</v>
       </c>
       <c r="F13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="G14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="G15" s="58" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="G16" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -3789,43 +3799,43 @@
   <sheetData>
     <row r="1" spans="2:14" s="21" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="B1" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="E1" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="F1" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="J1" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="K1" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="L1" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="M1" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="N1" s="19" t="s">
         <v>142</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="2" spans="2:14" ht="174" x14ac:dyDescent="0.35">
@@ -3836,22 +3846,22 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" t="s">
         <v>155</v>
-      </c>
-      <c r="E2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F2" t="s">
-        <v>157</v>
       </c>
       <c r="G2">
         <v>2024</v>
       </c>
       <c r="I2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K2" s="61" t="s">
         <v>158</v>
-      </c>
-      <c r="K2" s="61" t="s">
-        <v>160</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
